--- a/graficos/burdown/Gráfico de BurnDown.xlsx
+++ b/graficos/burdown/Gráfico de BurnDown.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30023"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E996FF0F-73AC-4E40-A378-C9A02B5C1168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andra\Documents\SPTECH\WineSense-Negocio\graficos\burdown\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{326FC3A1-0C1D-485E-97B7-F73E0192A525}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -31,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>Pontos a serem entregues</t>
   </si>
@@ -91,12 +96,15 @@
   <si>
     <t>Dias: 81 até 120</t>
   </si>
+  <si>
+    <t>89</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -266,7 +274,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="pt-BR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -764,7 +772,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Planilha1!G7:G127</c:f>
+              <c:f>Planilha1!$G$7:$G$127</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="121"/>
@@ -1010,6 +1018,126 @@
                 </c:pt>
                 <c:pt idx="80">
                   <c:v>89</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>76</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>68</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>68</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>47</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1786,16 +1914,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>676275</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>5714</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>15240</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>2009775</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
+      <xdr:colOff>2072639</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>13335</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1824,9 +1952,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office 2013 - 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1864,7 +1992,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1970,7 +2098,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2112,7 +2240,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2121,21 +2249,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O127"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.7109375" customWidth="1"/>
-    <col min="4" max="4" width="9.28515625" customWidth="1"/>
-    <col min="5" max="5" width="6.5703125" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" customWidth="1"/>
-    <col min="7" max="7" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.28515625" customWidth="1"/>
-    <col min="9" max="9" width="29.28515625" customWidth="1"/>
-    <col min="10" max="10" width="32.42578125" customWidth="1"/>
-    <col min="11" max="11" width="30.28515625" customWidth="1"/>
+    <col min="1" max="1" width="23.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.6640625" customWidth="1"/>
+    <col min="4" max="4" width="9.33203125" customWidth="1"/>
+    <col min="5" max="5" width="6.5546875" customWidth="1"/>
+    <col min="6" max="6" width="12.44140625" customWidth="1"/>
+    <col min="7" max="7" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.33203125" customWidth="1"/>
+    <col min="9" max="9" width="29.33203125" customWidth="1"/>
+    <col min="10" max="10" width="32.44140625" customWidth="1"/>
+    <col min="11" max="11" width="30.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2155,7 +2283,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -2176,7 +2304,7 @@
         <v>-41</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
@@ -2193,11 +2321,11 @@
         <v>120</v>
       </c>
       <c r="O3" s="10">
-        <f t="shared" ref="O3:O4" si="0">M3-N3</f>
+        <f t="shared" ref="O3" si="0">M3-N3</f>
         <v>72</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="15" customHeight="1">
+    <row r="4" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -2206,16 +2334,18 @@
       <c r="L4" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="M4" s="15"/>
+      <c r="M4" s="15" t="s">
+        <v>19</v>
+      </c>
       <c r="N4" s="11">
         <v>120</v>
       </c>
       <c r="O4" s="15">
         <f>M4-N4</f>
-        <v>-120</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" ht="27.75">
+        <v>-31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C6" s="4" t="s">
         <v>11</v>
       </c>
@@ -2242,7 +2372,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C7" s="13">
         <v>0</v>
       </c>
@@ -2259,7 +2389,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C8" s="12">
         <v>1</v>
       </c>
@@ -2278,7 +2408,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C9" s="12">
         <v>2</v>
       </c>
@@ -2297,7 +2427,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C10" s="12">
         <v>3</v>
       </c>
@@ -2316,7 +2446,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C11" s="12">
         <v>4</v>
       </c>
@@ -2335,7 +2465,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C12" s="12">
         <v>5</v>
       </c>
@@ -2354,7 +2484,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C13" s="12">
         <v>6</v>
       </c>
@@ -2373,7 +2503,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C14" s="12">
         <v>7</v>
       </c>
@@ -2392,7 +2522,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C15" s="12">
         <v>8</v>
       </c>
@@ -2411,7 +2541,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C16" s="12">
         <v>9</v>
       </c>
@@ -2430,7 +2560,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="17" spans="3:7">
+    <row r="17" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C17" s="12">
         <v>10</v>
       </c>
@@ -2449,7 +2579,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="18" spans="3:7">
+    <row r="18" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C18" s="12">
         <v>11</v>
       </c>
@@ -2468,7 +2598,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="19" spans="3:7">
+    <row r="19" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C19" s="12">
         <v>12</v>
       </c>
@@ -2487,7 +2617,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="20" spans="3:7">
+    <row r="20" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C20" s="12">
         <v>13</v>
       </c>
@@ -2506,7 +2636,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="21" spans="3:7">
+    <row r="21" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C21" s="12">
         <v>14</v>
       </c>
@@ -2525,7 +2655,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="22" spans="3:7">
+    <row r="22" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C22" s="12">
         <v>15</v>
       </c>
@@ -2544,7 +2674,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="23" spans="3:7">
+    <row r="23" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C23" s="12">
         <v>16</v>
       </c>
@@ -2563,7 +2693,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="24" spans="3:7">
+    <row r="24" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C24" s="12">
         <v>17</v>
       </c>
@@ -2582,7 +2712,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="25" spans="3:7">
+    <row r="25" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C25" s="12">
         <v>18</v>
       </c>
@@ -2601,7 +2731,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="26" spans="3:7">
+    <row r="26" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C26" s="12">
         <v>19</v>
       </c>
@@ -2620,7 +2750,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="27" spans="3:7">
+    <row r="27" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C27" s="12">
         <v>20</v>
       </c>
@@ -2639,7 +2769,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="28" spans="3:7">
+    <row r="28" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C28" s="12">
         <v>21</v>
       </c>
@@ -2658,7 +2788,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="29" spans="3:7">
+    <row r="29" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C29" s="12">
         <v>22</v>
       </c>
@@ -2677,7 +2807,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="30" spans="3:7">
+    <row r="30" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C30" s="12">
         <v>23</v>
       </c>
@@ -2696,7 +2826,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="31" spans="3:7">
+    <row r="31" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C31" s="12">
         <v>24</v>
       </c>
@@ -2715,7 +2845,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="32" spans="3:7">
+    <row r="32" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C32" s="12">
         <v>25</v>
       </c>
@@ -2734,7 +2864,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="33" spans="3:10">
+    <row r="33" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C33" s="12">
         <v>26</v>
       </c>
@@ -2753,7 +2883,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="34" spans="3:10">
+    <row r="34" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C34" s="12">
         <v>27</v>
       </c>
@@ -2772,7 +2902,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="35" spans="3:10">
+    <row r="35" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C35" s="12">
         <v>28</v>
       </c>
@@ -2792,7 +2922,7 @@
       </c>
       <c r="J35" s="17"/>
     </row>
-    <row r="36" spans="3:10">
+    <row r="36" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C36" s="12">
         <v>29</v>
       </c>
@@ -2811,7 +2941,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="37" spans="3:10">
+    <row r="37" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C37" s="12">
         <v>30</v>
       </c>
@@ -2830,7 +2960,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="38" spans="3:10">
+    <row r="38" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C38" s="12">
         <v>31</v>
       </c>
@@ -2849,7 +2979,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="39" spans="3:10">
+    <row r="39" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C39" s="12">
         <v>32</v>
       </c>
@@ -2868,7 +2998,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="40" spans="3:10">
+    <row r="40" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C40" s="12">
         <v>33</v>
       </c>
@@ -2887,7 +3017,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="41" spans="3:10">
+    <row r="41" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C41" s="12">
         <v>34</v>
       </c>
@@ -2906,7 +3036,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="42" spans="3:10">
+    <row r="42" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C42" s="12">
         <v>35</v>
       </c>
@@ -2925,7 +3055,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="43" spans="3:10">
+    <row r="43" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C43" s="12">
         <v>36</v>
       </c>
@@ -2944,7 +3074,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="44" spans="3:10">
+    <row r="44" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C44" s="12">
         <v>37</v>
       </c>
@@ -2963,7 +3093,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="45" spans="3:10">
+    <row r="45" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C45" s="12">
         <v>38</v>
       </c>
@@ -2982,7 +3112,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="46" spans="3:10">
+    <row r="46" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C46" s="12">
         <v>39</v>
       </c>
@@ -3001,7 +3131,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="47" spans="3:10">
+    <row r="47" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C47" s="12">
         <v>40</v>
       </c>
@@ -3020,7 +3150,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="48" spans="3:10">
+    <row r="48" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C48" s="10">
         <v>41</v>
       </c>
@@ -3039,7 +3169,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="49" spans="3:7">
+    <row r="49" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C49" s="10">
         <v>42</v>
       </c>
@@ -3058,7 +3188,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="50" spans="3:7">
+    <row r="50" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C50" s="10">
         <v>43</v>
       </c>
@@ -3077,7 +3207,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="51" spans="3:7">
+    <row r="51" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C51" s="10">
         <v>44</v>
       </c>
@@ -3096,7 +3226,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="52" spans="3:7">
+    <row r="52" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C52" s="10">
         <v>45</v>
       </c>
@@ -3115,7 +3245,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="53" spans="3:7">
+    <row r="53" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C53" s="10">
         <v>46</v>
       </c>
@@ -3134,7 +3264,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="54" spans="3:7">
+    <row r="54" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C54" s="10">
         <v>47</v>
       </c>
@@ -3153,7 +3283,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="55" spans="3:7">
+    <row r="55" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C55" s="10">
         <v>48</v>
       </c>
@@ -3172,7 +3302,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="56" spans="3:7">
+    <row r="56" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C56" s="10">
         <v>49</v>
       </c>
@@ -3191,7 +3321,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="57" spans="3:7">
+    <row r="57" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C57" s="10">
         <v>50</v>
       </c>
@@ -3210,7 +3340,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="58" spans="3:7">
+    <row r="58" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C58" s="10">
         <v>51</v>
       </c>
@@ -3229,7 +3359,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="59" spans="3:7">
+    <row r="59" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C59" s="10">
         <v>52</v>
       </c>
@@ -3248,7 +3378,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="60" spans="3:7">
+    <row r="60" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C60" s="10">
         <v>53</v>
       </c>
@@ -3267,7 +3397,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="61" spans="3:7">
+    <row r="61" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C61" s="10">
         <v>54</v>
       </c>
@@ -3286,7 +3416,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="62" spans="3:7">
+    <row r="62" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C62" s="10">
         <v>55</v>
       </c>
@@ -3305,7 +3435,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="63" spans="3:7">
+    <row r="63" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C63" s="10">
         <v>56</v>
       </c>
@@ -3324,7 +3454,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="64" spans="3:7">
+    <row r="64" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C64" s="10">
         <v>57</v>
       </c>
@@ -3343,7 +3473,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="65" spans="3:9">
+    <row r="65" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C65" s="10">
         <v>58</v>
       </c>
@@ -3362,7 +3492,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="66" spans="3:9">
+    <row r="66" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C66" s="10">
         <v>59</v>
       </c>
@@ -3381,7 +3511,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="67" spans="3:9">
+    <row r="67" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C67" s="10">
         <v>60</v>
       </c>
@@ -3400,7 +3530,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="68" spans="3:9">
+    <row r="68" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C68" s="10">
         <v>61</v>
       </c>
@@ -3419,7 +3549,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="69" spans="3:9">
+    <row r="69" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C69" s="10">
         <v>62</v>
       </c>
@@ -3438,7 +3568,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="70" spans="3:9">
+    <row r="70" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C70" s="10">
         <v>63</v>
       </c>
@@ -3457,7 +3587,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="71" spans="3:9">
+    <row r="71" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C71" s="10">
         <v>64</v>
       </c>
@@ -3476,7 +3606,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="72" spans="3:9">
+    <row r="72" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C72" s="10">
         <v>65</v>
       </c>
@@ -3495,7 +3625,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="73" spans="3:9">
+    <row r="73" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C73" s="10">
         <v>66</v>
       </c>
@@ -3510,11 +3640,11 @@
         <v>3</v>
       </c>
       <c r="G73" s="10">
-        <f t="shared" ref="G73:G127" si="4">G72-F73</f>
+        <f t="shared" ref="G73:G87" si="4">G72-F73</f>
         <v>144</v>
       </c>
     </row>
-    <row r="74" spans="3:9">
+    <row r="74" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C74" s="10">
         <v>67</v>
       </c>
@@ -3533,7 +3663,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="75" spans="3:9">
+    <row r="75" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C75" s="10">
         <v>68</v>
       </c>
@@ -3552,7 +3682,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="76" spans="3:9">
+    <row r="76" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C76" s="10">
         <v>69</v>
       </c>
@@ -3571,7 +3701,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="77" spans="3:9">
+    <row r="77" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C77" s="10">
         <v>70</v>
       </c>
@@ -3590,7 +3720,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="78" spans="3:9">
+    <row r="78" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C78" s="10">
         <v>71</v>
       </c>
@@ -3610,7 +3740,7 @@
       </c>
       <c r="I78" s="17"/>
     </row>
-    <row r="79" spans="3:9">
+    <row r="79" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C79" s="10">
         <v>72</v>
       </c>
@@ -3629,7 +3759,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="80" spans="3:9">
+    <row r="80" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C80" s="10">
         <v>73</v>
       </c>
@@ -3648,7 +3778,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="81" spans="3:7">
+    <row r="81" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C81" s="10">
         <v>74</v>
       </c>
@@ -3667,7 +3797,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="82" spans="3:7">
+    <row r="82" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C82" s="10">
         <v>75</v>
       </c>
@@ -3686,7 +3816,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="83" spans="3:7">
+    <row r="83" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C83" s="10">
         <v>76</v>
       </c>
@@ -3705,7 +3835,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="84" spans="3:7">
+    <row r="84" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C84" s="10">
         <v>77</v>
       </c>
@@ -3724,7 +3854,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="85" spans="3:7">
+    <row r="85" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C85" s="10">
         <v>78</v>
       </c>
@@ -3743,7 +3873,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="86" spans="3:7">
+    <row r="86" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C86" s="10">
         <v>79</v>
       </c>
@@ -3762,7 +3892,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="87" spans="3:7">
+    <row r="87" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C87" s="10">
         <v>80</v>
       </c>
@@ -3781,7 +3911,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="88" spans="3:7">
+    <row r="88" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C88" s="11">
         <v>81</v>
       </c>
@@ -3792,10 +3922,14 @@
         <f t="shared" si="3"/>
         <v>117</v>
       </c>
-      <c r="F88" s="11"/>
-      <c r="G88" s="11"/>
-    </row>
-    <row r="89" spans="3:7">
+      <c r="F88" s="11">
+        <v>13</v>
+      </c>
+      <c r="G88" s="11">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="89" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C89" s="11">
         <v>82</v>
       </c>
@@ -3806,10 +3940,14 @@
         <f t="shared" si="3"/>
         <v>114</v>
       </c>
-      <c r="F89" s="11"/>
-      <c r="G89" s="11"/>
-    </row>
-    <row r="90" spans="3:7">
+      <c r="F89" s="11">
+        <v>8</v>
+      </c>
+      <c r="G89" s="11">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="90" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C90" s="11">
         <v>83</v>
       </c>
@@ -3820,10 +3958,14 @@
         <f t="shared" si="3"/>
         <v>111</v>
       </c>
-      <c r="F90" s="11"/>
-      <c r="G90" s="11"/>
-    </row>
-    <row r="91" spans="3:7">
+      <c r="F90" s="11">
+        <v>0</v>
+      </c>
+      <c r="G90" s="11">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="91" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C91" s="11">
         <v>84</v>
       </c>
@@ -3834,10 +3976,14 @@
         <f t="shared" si="3"/>
         <v>108</v>
       </c>
-      <c r="F91" s="11"/>
-      <c r="G91" s="11"/>
-    </row>
-    <row r="92" spans="3:7">
+      <c r="F91" s="11">
+        <v>3</v>
+      </c>
+      <c r="G91" s="11">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="92" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C92" s="11">
         <v>85</v>
       </c>
@@ -3848,10 +3994,14 @@
         <f t="shared" si="3"/>
         <v>105</v>
       </c>
-      <c r="F92" s="11"/>
-      <c r="G92" s="11"/>
-    </row>
-    <row r="93" spans="3:7">
+      <c r="F92" s="11">
+        <v>5</v>
+      </c>
+      <c r="G92" s="11">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="93" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C93" s="11">
         <v>86</v>
       </c>
@@ -3862,10 +4012,14 @@
         <f t="shared" si="3"/>
         <v>102</v>
       </c>
-      <c r="F93" s="11"/>
-      <c r="G93" s="11"/>
-    </row>
-    <row r="94" spans="3:7">
+      <c r="F93" s="11">
+        <v>0</v>
+      </c>
+      <c r="G93" s="11">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="94" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C94" s="11">
         <v>87</v>
       </c>
@@ -3876,10 +4030,14 @@
         <f t="shared" si="3"/>
         <v>99</v>
       </c>
-      <c r="F94" s="11"/>
-      <c r="G94" s="11"/>
-    </row>
-    <row r="95" spans="3:7">
+      <c r="F94" s="11">
+        <v>0</v>
+      </c>
+      <c r="G94" s="11">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="95" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C95" s="11">
         <v>88</v>
       </c>
@@ -3890,10 +4048,14 @@
         <f t="shared" si="3"/>
         <v>96</v>
       </c>
-      <c r="F95" s="11"/>
-      <c r="G95" s="11"/>
-    </row>
-    <row r="96" spans="3:7">
+      <c r="F95" s="11">
+        <v>13</v>
+      </c>
+      <c r="G95" s="11">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="96" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C96" s="11">
         <v>89</v>
       </c>
@@ -3904,10 +4066,14 @@
         <f t="shared" si="3"/>
         <v>93</v>
       </c>
-      <c r="F96" s="11"/>
-      <c r="G96" s="11"/>
-    </row>
-    <row r="97" spans="3:7">
+      <c r="F96" s="11">
+        <v>5</v>
+      </c>
+      <c r="G96" s="11">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="97" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C97" s="11">
         <v>90</v>
       </c>
@@ -3918,10 +4084,14 @@
         <f t="shared" si="3"/>
         <v>90</v>
       </c>
-      <c r="F97" s="11"/>
-      <c r="G97" s="11"/>
-    </row>
-    <row r="98" spans="3:7">
+      <c r="F97" s="11">
+        <v>0</v>
+      </c>
+      <c r="G97" s="11">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="98" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C98" s="11">
         <v>91</v>
       </c>
@@ -3932,10 +4102,14 @@
         <f t="shared" si="3"/>
         <v>87</v>
       </c>
-      <c r="F98" s="11"/>
-      <c r="G98" s="11"/>
-    </row>
-    <row r="99" spans="3:7">
+      <c r="F98" s="11">
+        <v>3</v>
+      </c>
+      <c r="G98" s="11">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="99" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C99" s="11">
         <v>92</v>
       </c>
@@ -3946,10 +4120,14 @@
         <f t="shared" si="3"/>
         <v>84</v>
       </c>
-      <c r="F99" s="11"/>
-      <c r="G99" s="11"/>
-    </row>
-    <row r="100" spans="3:7">
+      <c r="F99" s="11">
+        <v>3</v>
+      </c>
+      <c r="G99" s="11">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="100" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C100" s="11">
         <v>93</v>
       </c>
@@ -3960,10 +4138,14 @@
         <f t="shared" si="3"/>
         <v>81</v>
       </c>
-      <c r="F100" s="11"/>
-      <c r="G100" s="11"/>
-    </row>
-    <row r="101" spans="3:7">
+      <c r="F100" s="11">
+        <v>0</v>
+      </c>
+      <c r="G100" s="11">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="101" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C101" s="11">
         <v>94</v>
       </c>
@@ -3974,10 +4156,14 @@
         <f t="shared" si="3"/>
         <v>78</v>
       </c>
-      <c r="F101" s="11"/>
-      <c r="G101" s="11"/>
-    </row>
-    <row r="102" spans="3:7">
+      <c r="F101" s="11">
+        <v>5</v>
+      </c>
+      <c r="G101" s="11">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="102" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C102" s="11">
         <v>95</v>
       </c>
@@ -3988,10 +4174,14 @@
         <f t="shared" si="3"/>
         <v>75</v>
       </c>
-      <c r="F102" s="11"/>
-      <c r="G102" s="11"/>
-    </row>
-    <row r="103" spans="3:7">
+      <c r="F102" s="11">
+        <v>0</v>
+      </c>
+      <c r="G102" s="11">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="103" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C103" s="11">
         <v>96</v>
       </c>
@@ -4002,10 +4192,14 @@
         <f t="shared" si="3"/>
         <v>72</v>
       </c>
-      <c r="F103" s="11"/>
-      <c r="G103" s="11"/>
-    </row>
-    <row r="104" spans="3:7">
+      <c r="F103" s="11">
+        <v>0</v>
+      </c>
+      <c r="G103" s="11">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="104" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C104" s="11">
         <v>97</v>
       </c>
@@ -4016,10 +4210,14 @@
         <f t="shared" si="3"/>
         <v>69</v>
       </c>
-      <c r="F104" s="11"/>
-      <c r="G104" s="11"/>
-    </row>
-    <row r="105" spans="3:7">
+      <c r="F104" s="11">
+        <v>3</v>
+      </c>
+      <c r="G104" s="11">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="105" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C105" s="11">
         <v>98</v>
       </c>
@@ -4030,10 +4228,14 @@
         <f t="shared" si="3"/>
         <v>66</v>
       </c>
-      <c r="F105" s="11"/>
-      <c r="G105" s="11"/>
-    </row>
-    <row r="106" spans="3:7">
+      <c r="F105" s="11">
+        <v>0</v>
+      </c>
+      <c r="G105" s="11">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="106" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C106" s="11">
         <v>99</v>
       </c>
@@ -4044,10 +4246,14 @@
         <f t="shared" si="3"/>
         <v>63</v>
       </c>
-      <c r="F106" s="11"/>
-      <c r="G106" s="11"/>
-    </row>
-    <row r="107" spans="3:7">
+      <c r="F106" s="11">
+        <v>0</v>
+      </c>
+      <c r="G106" s="11">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="107" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C107" s="11">
         <v>100</v>
       </c>
@@ -4058,10 +4264,14 @@
         <f t="shared" si="3"/>
         <v>60</v>
       </c>
-      <c r="F107" s="11"/>
-      <c r="G107" s="11"/>
-    </row>
-    <row r="108" spans="3:7">
+      <c r="F107" s="11">
+        <v>0</v>
+      </c>
+      <c r="G107" s="11">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="108" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C108" s="11">
         <v>101</v>
       </c>
@@ -4072,10 +4282,14 @@
         <f t="shared" si="3"/>
         <v>57</v>
       </c>
-      <c r="F108" s="11"/>
-      <c r="G108" s="11"/>
-    </row>
-    <row r="109" spans="3:7">
+      <c r="F108" s="11">
+        <v>5</v>
+      </c>
+      <c r="G108" s="11">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="109" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C109" s="11">
         <v>102</v>
       </c>
@@ -4086,10 +4300,14 @@
         <f t="shared" si="3"/>
         <v>54</v>
       </c>
-      <c r="F109" s="11"/>
-      <c r="G109" s="11"/>
-    </row>
-    <row r="110" spans="3:7">
+      <c r="F109" s="11">
+        <v>0</v>
+      </c>
+      <c r="G109" s="11">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="110" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C110" s="11">
         <v>103</v>
       </c>
@@ -4100,10 +4318,14 @@
         <f t="shared" si="3"/>
         <v>51</v>
       </c>
-      <c r="F110" s="11"/>
-      <c r="G110" s="11"/>
-    </row>
-    <row r="111" spans="3:7">
+      <c r="F110" s="11">
+        <v>3</v>
+      </c>
+      <c r="G110" s="11">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="111" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C111" s="11">
         <v>104</v>
       </c>
@@ -4114,10 +4336,14 @@
         <f t="shared" si="3"/>
         <v>48</v>
       </c>
-      <c r="F111" s="11"/>
-      <c r="G111" s="11"/>
-    </row>
-    <row r="112" spans="3:7">
+      <c r="F111" s="11">
+        <v>3</v>
+      </c>
+      <c r="G111" s="11">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="112" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C112" s="11">
         <v>105</v>
       </c>
@@ -4128,10 +4354,14 @@
         <f t="shared" si="3"/>
         <v>45</v>
       </c>
-      <c r="F112" s="11"/>
-      <c r="G112" s="11"/>
-    </row>
-    <row r="113" spans="3:7">
+      <c r="F112" s="11">
+        <v>0</v>
+      </c>
+      <c r="G112" s="11">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="113" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C113" s="11">
         <v>106</v>
       </c>
@@ -4142,10 +4372,14 @@
         <f t="shared" si="3"/>
         <v>42</v>
       </c>
-      <c r="F113" s="11"/>
-      <c r="G113" s="11"/>
-    </row>
-    <row r="114" spans="3:7">
+      <c r="F113" s="11">
+        <v>8</v>
+      </c>
+      <c r="G113" s="11">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="114" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C114" s="11">
         <v>107</v>
       </c>
@@ -4156,10 +4390,14 @@
         <f t="shared" si="3"/>
         <v>39</v>
       </c>
-      <c r="F114" s="11"/>
-      <c r="G114" s="11"/>
-    </row>
-    <row r="115" spans="3:7">
+      <c r="F114" s="11">
+        <v>0</v>
+      </c>
+      <c r="G114" s="11">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="115" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C115" s="11">
         <v>108</v>
       </c>
@@ -4170,10 +4408,14 @@
         <f t="shared" si="3"/>
         <v>36</v>
       </c>
-      <c r="F115" s="11"/>
-      <c r="G115" s="11"/>
-    </row>
-    <row r="116" spans="3:7">
+      <c r="F115" s="11">
+        <v>0</v>
+      </c>
+      <c r="G115" s="11">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="116" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C116" s="11">
         <v>109</v>
       </c>
@@ -4184,10 +4426,14 @@
         <f t="shared" si="3"/>
         <v>33</v>
       </c>
-      <c r="F116" s="11"/>
-      <c r="G116" s="11"/>
-    </row>
-    <row r="117" spans="3:7">
+      <c r="F116" s="11">
+        <v>3</v>
+      </c>
+      <c r="G116" s="11">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="117" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C117" s="11">
         <v>110</v>
       </c>
@@ -4198,10 +4444,14 @@
         <f t="shared" si="3"/>
         <v>30</v>
       </c>
-      <c r="F117" s="11"/>
-      <c r="G117" s="11"/>
-    </row>
-    <row r="118" spans="3:7">
+      <c r="F117" s="11">
+        <v>0</v>
+      </c>
+      <c r="G117" s="11">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="118" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C118" s="11">
         <v>111</v>
       </c>
@@ -4212,10 +4462,14 @@
         <f t="shared" si="3"/>
         <v>27</v>
       </c>
-      <c r="F118" s="11"/>
-      <c r="G118" s="11"/>
-    </row>
-    <row r="119" spans="3:7">
+      <c r="F118" s="11">
+        <v>0</v>
+      </c>
+      <c r="G118" s="11">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="119" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C119" s="11">
         <v>112</v>
       </c>
@@ -4226,10 +4480,14 @@
         <f t="shared" si="3"/>
         <v>24</v>
       </c>
-      <c r="F119" s="11"/>
-      <c r="G119" s="11"/>
-    </row>
-    <row r="120" spans="3:7">
+      <c r="F119" s="11">
+        <v>3</v>
+      </c>
+      <c r="G119" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="120" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C120" s="11">
         <v>113</v>
       </c>
@@ -4240,10 +4498,14 @@
         <f t="shared" si="3"/>
         <v>21</v>
       </c>
-      <c r="F120" s="11"/>
-      <c r="G120" s="11"/>
-    </row>
-    <row r="121" spans="3:7">
+      <c r="F120" s="11">
+        <v>0</v>
+      </c>
+      <c r="G120" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="121" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C121" s="11">
         <v>114</v>
       </c>
@@ -4254,10 +4516,14 @@
         <f t="shared" si="3"/>
         <v>18</v>
       </c>
-      <c r="F121" s="11"/>
-      <c r="G121" s="11"/>
-    </row>
-    <row r="122" spans="3:7">
+      <c r="F121" s="11">
+        <v>0</v>
+      </c>
+      <c r="G121" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="122" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C122" s="11">
         <v>115</v>
       </c>
@@ -4268,10 +4534,14 @@
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
-      <c r="F122" s="11"/>
-      <c r="G122" s="11"/>
-    </row>
-    <row r="123" spans="3:7">
+      <c r="F122" s="11">
+        <v>0</v>
+      </c>
+      <c r="G122" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="123" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C123" s="11">
         <v>116</v>
       </c>
@@ -4282,10 +4552,14 @@
         <f t="shared" si="3"/>
         <v>12</v>
       </c>
-      <c r="F123" s="11"/>
-      <c r="G123" s="11"/>
-    </row>
-    <row r="124" spans="3:7">
+      <c r="F123" s="11">
+        <v>0</v>
+      </c>
+      <c r="G123" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="124" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C124" s="11">
         <v>117</v>
       </c>
@@ -4296,10 +4570,14 @@
         <f t="shared" si="3"/>
         <v>9</v>
       </c>
-      <c r="F124" s="11"/>
-      <c r="G124" s="11"/>
-    </row>
-    <row r="125" spans="3:7">
+      <c r="F124" s="11">
+        <v>3</v>
+      </c>
+      <c r="G124" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C125" s="11">
         <v>118</v>
       </c>
@@ -4310,10 +4588,14 @@
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="F125" s="11"/>
-      <c r="G125" s="11"/>
-    </row>
-    <row r="126" spans="3:7">
+      <c r="F125" s="11">
+        <v>0</v>
+      </c>
+      <c r="G125" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C126" s="11">
         <v>119</v>
       </c>
@@ -4324,10 +4606,14 @@
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="F126" s="11"/>
-      <c r="G126" s="11"/>
-    </row>
-    <row r="127" spans="3:7">
+      <c r="F126" s="11">
+        <v>0</v>
+      </c>
+      <c r="G126" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C127" s="11">
         <v>120</v>
       </c>
@@ -4338,8 +4624,12 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F127" s="11"/>
-      <c r="G127" s="11"/>
+      <c r="F127" s="11">
+        <v>0</v>
+      </c>
+      <c r="G127" s="11">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
